--- a/314e-ig/output/StructureDefinition-organization-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-organization-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-organization-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-organization-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-organization-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-organization-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-organization-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-organization-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$68</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="518">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>314e-constrained Organization profile derived from US Core Organization.
+    <t>314e-constrained Organization profile derived from QI-Core Organization.
 This profile applies 314e-defined extensions and uses 314e datatype profiles
 where applicable.</t>
   </si>
@@ -116,7 +116,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization</t>
+    <t>http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -601,6 +601,293 @@
 us-core-19:NAIC must be 5 digits {value.matches('^[0-9]{5}$')}</t>
   </si>
   <si>
+    <t>Organization.identifier:ccn</t>
+  </si>
+  <si>
+    <t>ccn</t>
+  </si>
+  <si>
+    <t>(QI) CMS Certification Number</t>
+  </si>
+  <si>
+    <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://terminology.hl7.org/NamingSystem/CMSCertificationNumber"/&gt;
+&lt;/valueIdentifier&gt;</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ccn.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ccn.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ccn.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>(QI) usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ccn.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ccn.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>./IdentifierType</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ccn.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier.value</t>
+  </si>
+  <si>
+    <t>(QI) The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>./Value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ccn.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ccn.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>./IdentifierIssuingAuthority</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein</t>
+  </si>
+  <si>
+    <t>ein</t>
+  </si>
+  <si>
+    <t>(QI) Employer Identification Number</t>
+  </si>
+  <si>
+    <t>There is not a general Tax Identifier Numer (TIN) OID. There is an SSN, a PTIN, and an ITIN, but no TIN generally. So the only slice specified here is EIN, if consumers determine a need for an SSN, submit a comment to that effect.</t>
+  </si>
+  <si>
+    <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="urn:oid:2.16.840.1.113883.4.4"/&gt;
+&lt;/valueIdentifier&gt;</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ein.assigner</t>
+  </si>
+  <si>
     <t>Organization.active</t>
   </si>
   <si>
@@ -643,7 +930,7 @@
 </t>
   </si>
   <si>
-    <t>Kind of organization</t>
+    <t>(QI) Kind of organization</t>
   </si>
   <si>
     <t>The kind(s) of organization that this is.</t>
@@ -657,10 +944,7 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Used to categorize the organization.</t>
+    <t>Used to categorize the organization</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
@@ -672,17 +956,10 @@
     <t>.code</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>FiveWs.class</t>
   </si>
   <si>
     <t>Organization.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Name used for the organization</t>
@@ -761,30 +1038,9 @@
     <t>Organization.telecom.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Organization.telecom.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Organization.telecom.system</t>
   </si>
   <si>
@@ -792,9 +1048,6 @@
   </si>
   <si>
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
@@ -843,9 +1096,6 @@
     <t>./url</t>
   </si>
   <si>
-    <t>./Value</t>
-  </si>
-  <si>
     <t>Organization.telecom.use</t>
   </si>
   <si>
@@ -901,10 +1151,6 @@
     <t>Organization.telecom.period</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
     <t>Time period when the contact point was/is in use</t>
   </si>
   <si>
@@ -915,9 +1161,6 @@
   </si>
   <si>
     <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -1146,9 +1389,6 @@
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Two letter USPS alphabetic codes.</t>
@@ -1248,7 +1488,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1391,7 +1631,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/endpoint-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1718,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.83984375" customWidth="true" bestFit="true"/>
@@ -1731,7 +1971,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="71.1171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="106.66015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1740,12 +1980,12 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="34.7578125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.80859375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.2578125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="85.70703125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="46.1796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
@@ -1757,7 +1997,7 @@
     <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="92.15234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.64453125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="89.40625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="189.36328125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.45703125" customWidth="true" bestFit="true"/>
   </cols>
@@ -3487,15 +3727,17 @@
         <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="D16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>86</v>
@@ -3504,38 +3746,36 @@
         <v>87</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="P16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="N16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="P16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="R16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="T16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3573,39 +3813,39 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>192</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3616,7 +3856,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3625,23 +3865,19 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3665,13 +3901,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3689,75 +3925,73 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
+      <c r="A18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="AG17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>207</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3793,40 +4027,40 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -3834,10 +4068,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3845,34 +4079,34 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3897,13 +4131,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3921,13 +4155,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3936,10 +4170,10 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -3948,12 +4182,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3964,31 +4198,31 @@
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4013,13 +4247,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4043,22 +4277,22 @@
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>227</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
@@ -4066,10 +4300,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4089,19 +4323,23 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4113,7 +4351,7 @@
         <v>20</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>20</v>
@@ -4149,7 +4387,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4161,16 +4399,16 @@
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -4178,21 +4416,21 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4201,19 +4439,19 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4227,7 +4465,7 @@
         <v>20</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="U22" t="s" s="2">
         <v>20</v>
@@ -4251,16 +4489,16 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>239</v>
@@ -4269,33 +4507,33 @@
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4309,7 +4547,7 @@
         <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -4318,13 +4556,13 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4351,13 +4589,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4375,7 +4613,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4384,30 +4622,30 @@
         <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4421,7 +4659,7 @@
         <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -4430,20 +4668,18 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4491,7 +4727,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4506,26 +4742,28 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
@@ -4537,28 +4775,28 @@
         <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>154</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>264</v>
+        <v>156</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4568,7 +4806,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -4583,13 +4821,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4607,39 +4845,39 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>151</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>268</v>
+        <v>159</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>160</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>161</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>20</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>187</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4659,20 +4897,18 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>272</v>
+        <v>188</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>189</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4721,7 +4957,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>191</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4733,13 +4969,13 @@
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>204</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4750,21 +4986,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>194</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4773,18 +5009,20 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>278</v>
+        <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4821,51 +5059,51 @@
         <v>20</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>198</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>283</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>284</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4873,34 +5111,34 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="I28" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>285</v>
+        <v>106</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>201</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4925,13 +5163,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -4949,28 +5187,28 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>291</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>292</v>
+        <v>129</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>293</v>
+        <v>209</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -4978,10 +5216,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>295</v>
+        <v>211</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5001,19 +5239,23 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5037,13 +5279,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5061,7 +5303,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5073,13 +5315,13 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5090,21 +5332,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>223</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5113,21 +5355,23 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5139,7 +5383,7 @@
         <v>20</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>20</v>
@@ -5163,40 +5407,40 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>134</v>
+        <v>20</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>20</v>
+        <v>230</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -5204,10 +5448,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5215,7 +5459,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>86</v>
@@ -5224,26 +5468,24 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5255,7 +5497,7 @@
         <v>20</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>302</v>
+        <v>238</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>20</v>
@@ -5267,13 +5509,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>304</v>
+        <v>20</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5291,7 +5533,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>239</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5306,13 +5548,13 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>306</v>
+        <v>240</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>20</v>
@@ -5320,10 +5562,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>244</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5346,17 +5588,15 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5369,7 +5609,7 @@
         <v>20</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>20</v>
@@ -5381,13 +5621,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5405,7 +5645,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5420,13 +5660,13 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5434,10 +5674,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5460,20 +5700,18 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5485,7 +5723,7 @@
         <v>20</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>20</v>
@@ -5521,7 +5759,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>258</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5536,13 +5774,13 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>324</v>
+        <v>259</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>325</v>
+        <v>260</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5550,10 +5788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5561,35 +5799,41 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>327</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>87</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q34" s="2"/>
+      <c r="Q34" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="R34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5597,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>330</v>
+        <v>20</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>20</v>
@@ -5633,13 +5877,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>275</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5648,38 +5892,38 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>332</v>
+        <v>282</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>20</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>336</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
@@ -5688,16 +5932,20 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>207</v>
+        <v>287</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5709,7 +5957,7 @@
         <v>20</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>20</v>
@@ -5721,13 +5969,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>292</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5745,13 +5993,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5760,38 +6008,38 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>342</v>
+        <v>295</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>343</v>
+        <v>192</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -5800,18 +6048,20 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5823,7 +6073,7 @@
         <v>20</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>20</v>
@@ -5859,7 +6109,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5868,62 +6118,66 @@
         <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>351</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>352</v>
+        <v>303</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>20</v>
+        <v>304</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5935,7 +6189,7 @@
         <v>20</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>20</v>
@@ -5947,13 +6201,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5971,13 +6225,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -5986,13 +6240,13 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>363</v>
+        <v>303</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6000,21 +6254,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>366</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>87</v>
@@ -6023,19 +6277,23 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>207</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>367</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6047,7 +6305,7 @@
         <v>20</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>369</v>
+        <v>20</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>20</v>
@@ -6083,39 +6341,39 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6129,26 +6387,24 @@
         <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>375</v>
+        <v>189</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6197,7 +6453,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>378</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6209,16 +6465,16 @@
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>380</v>
+        <v>192</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6226,21 +6482,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6249,21 +6505,21 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>278</v>
+        <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>383</v>
+        <v>195</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6275,7 +6531,7 @@
         <v>20</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>20</v>
@@ -6299,51 +6555,51 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>387</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>388</v>
+        <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>283</v>
+        <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>389</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>389</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6357,7 +6613,7 @@
         <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>20</v>
@@ -6366,18 +6622,16 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>106</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>391</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>392</v>
+        <v>325</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>393</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6401,13 +6655,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6425,7 +6679,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>389</v>
+        <v>328</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6434,30 +6688,30 @@
         <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>189</v>
+        <v>330</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>204</v>
+        <v>332</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>333</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6468,31 +6722,31 @@
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>396</v>
+        <v>188</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>397</v>
+        <v>334</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>398</v>
+        <v>335</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>399</v>
+        <v>336</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>400</v>
+        <v>337</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6541,13 +6795,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -6556,13 +6810,13 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>401</v>
+        <v>340</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6570,10 +6824,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>402</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6590,22 +6844,26 @@
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>207</v>
+        <v>106</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>232</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6629,13 +6887,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6653,7 +6911,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>234</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6665,16 +6923,16 @@
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>204</v>
+        <v>350</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>20</v>
+        <v>351</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6682,21 +6940,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6705,19 +6963,19 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>131</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>236</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>237</v>
+        <v>355</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>148</v>
+        <v>356</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6767,25 +7025,25 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>239</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
@@ -6796,46 +7054,42 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>405</v>
+        <v>20</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>406</v>
+        <v>359</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -6883,39 +7137,39 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>129</v>
+        <v>362</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>20</v>
+        <v>251</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6926,10 +7180,10 @@
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
@@ -6938,17 +7192,19 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>194</v>
+        <v>364</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>410</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>412</v>
+        <v>368</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -6973,13 +7229,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>413</v>
+        <v>20</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>414</v>
+        <v>20</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -6997,28 +7253,28 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>409</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>370</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>415</v>
+        <v>372</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7026,10 +7282,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>374</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7052,18 +7308,16 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>417</v>
+        <v>188</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>418</v>
+        <v>189</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>419</v>
+        <v>190</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>420</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7111,7 +7365,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>416</v>
+        <v>191</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7123,13 +7377,13 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>422</v>
+        <v>192</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7140,14 +7394,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7166,18 +7420,18 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>424</v>
+        <v>195</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
@@ -7213,19 +7467,19 @@
         <v>20</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>423</v>
+        <v>198</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7237,13 +7491,13 @@
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>428</v>
+        <v>192</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7254,10 +7508,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>429</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>429</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7274,23 +7528,25 @@
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>285</v>
+        <v>106</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>430</v>
+        <v>377</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>432</v>
+        <v>380</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7303,7 +7559,7 @@
         <v>20</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>20</v>
+        <v>381</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>20</v>
@@ -7315,13 +7571,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>20</v>
+        <v>382</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7339,7 +7595,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7354,13 +7610,13 @@
         <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>433</v>
+        <v>385</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>434</v>
+        <v>350</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>20</v>
+        <v>386</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -7368,10 +7624,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7382,7 +7638,7 @@
         <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7391,21 +7647,21 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>436</v>
+        <v>106</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>437</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -7417,7 +7673,7 @@
         <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>20</v>
@@ -7429,13 +7685,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>20</v>
+        <v>392</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7453,13 +7709,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>394</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -7468,20 +7724,2068 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>204</v>
+        <v>350</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN50">
+  <autoFilter ref="A1:AN68">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7491,7 +9795,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI49">
+  <conditionalFormatting sqref="A2:AI67">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-organization-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-organization-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-organization-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-organization-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
